--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,562 @@
           <t>Asignado a</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Fechas críticas: Entrega de propuestas del 03 al 08 de julio de 2026; Fallos programados entre el 03 y 09 de julio de 2026. Vigencia del contrato: No especificado en el texto resumido.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Diversos bienes y servicios: material de oficina, impresión de libros, congresos y convenciones, arrendamiento de maquinaria de limpieza, evaluación de resultados FAISM, vehículos en general, lámparas de alumbrado público y una motoniveladora nueva. Modalidad de pago: No especificado.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Diversas instituciones: Policía Industrial Bancaria (Pachuca), Instituto Hidalguense de Educación (Pachuca), Municipio de Huejutla de Reyes (Palacio Municipal), Municipio de Mineral de la Reforma (Pachuquilla) y Municipio de Actopan (Calle Hidalgo No. 8, Col. Centro).</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria: 1 concepto (Material de Oficina) | IHE: 5 partidas totales (libros y congresos) | Huejutla: 3 partidas únicas (maquinaria, evaluación FAISM, vehículos) | Mineral de la Reforma: 2 partidas (lámparas suburbanas) | Actopan: 1 partida (motoniveladora nueva).</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Volumen operativo proyectado: No especificado. Se detalla el tipo de bien o servicio por licitación según las partidas indicadas.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Se menciona cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normativas constitucionales estatales. Requisitos específicos como NOMs o COFEPRIS no aparecen en el texto.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -595,12 +594,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -611,16 +604,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -653,7 +636,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -664,12 +646,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -680,16 +656,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -722,7 +688,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -733,24 +698,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -783,7 +730,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -794,24 +740,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -844,7 +772,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -855,12 +782,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -871,16 +792,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -913,7 +824,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -924,12 +834,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -940,16 +844,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -982,7 +876,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -993,24 +886,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1043,7 +918,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -1054,12 +928,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1105,9 +973,569 @@
           <t>Se menciona cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normativas constitucionales estatales. Requisitos específicos como NOMs o COFEPRIS no aparecen en el texto.</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Las fechas límite de entrega/apertura de propuestas varían entre el 03 y el 08 de julio de 2026. Los fallos están programados entre el 08 y el 09 de julio de 2026. Vigencia del contrato: No especificada en los resúmenes.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Diversos bienes y servicios: material de oficina (PIBEH), impresión de libros e organización de congresos (IHE), arrendamiento de maquinaria, evaluación FAISM y adquisición de vehículos (Huejutla), lámparas de alumbrado (Mineral de la Reforma), y motoniveladora (Actopan). Modalidad de pago y consumibles: No especificado.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria (Pachuca), Instituto Hidalguense de Educación (Pachuca), Municipio de Huejutla de Reyes (Palacio Municipal), Municipio de Mineral de la Reforma (Pachuquilla) y Municipio de Actopan (Calle Hidalgo No. 8, Col. Centro).</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>• PIBEH: Material de Oficina | 1 concepto
+• IHE: Impresión de libros | 2 partidas
+• IHE: Servicios de congresos | 3 partidas
+• Huejutla: Arrendamiento maquinaria | 1 partida
+• Huejutla: Evaluación FAISM | 1 partida
+• Huejutla: Vehículos en general | 1 partida
+• Mineral de la Reforma: Lámparas suburbanas | 2 partidas
+• Actopan: Motoniveladora nueva | 1 partida</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Volúmenes operativos y detalles técnicos específicos por partida no especificados en los resúmenes de convocatoria.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Se fundamenta en la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo. No se mencionan NOMs, licencias específicas o partnerships tecnológicos obligatorios.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,7 +1005,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1016,12 +1015,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1032,16 +1025,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1074,7 +1057,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1085,12 +1067,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1101,16 +1077,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1143,7 +1109,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1154,24 +1119,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1204,7 +1151,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1215,24 +1161,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1265,7 +1193,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1276,12 +1203,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1292,16 +1213,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1334,7 +1245,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1345,12 +1255,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1361,16 +1265,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1403,7 +1297,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -1414,24 +1307,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1464,7 +1339,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -1475,12 +1349,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1533,9 +1401,676 @@
           <t>Se fundamenta en la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo. No se mencionan NOMs, licencias específicas o partnerships tecnológicos obligatorios.</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Diversas licitaciones con apertura de propuestas entre el 03, 07 y 08 de julio de 2026. Fallos programados entre el 03, 08 y 09 de julio de 2026. Vigencia del contrato: No especificado en los resúmenes.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Diversos: material de oficina, servicios de impresión de libros, congresos y convenciones, arrendamiento de maquinaria, evaluación FAISM, adquisición de vehículo y lámparas de alumbrado público, y adquisición de una motoniveladora.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria (Pachuca), Instituto Hidalguense de Educación (Pachuca), Municipio de Huejutla de Reyes (Palacio Municipal), Municipio de Mineral de la Reforma (Pachuquilla), Municipio de Actopan (Calle Hidalgo No. 8, Centro).</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Ubicación | Cantidad y equipo | Características
+- PIBEH | 1 concepto | Material de oficina
+- IHE | 2 partidas | Servicio de impresión de libros
+- IHE | 3 partidas | Servicio de congresos y convenciones
+- Huejutla | Partida única | Arrendamiento maquinaria limpia pública
+- Huejutla | Partida única | Evaluación FAISM
+- Huejutla | Partida única | Vehículo en general
+- Mineral de la Reforma | 2 partidas | Lámparas suburbanas
+- Actopan | 1 partida | Motoniveladora nueva</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Volúmenes definidos por partidas según cada licitación, sin desglosar cantidades totales ni unidades de servicio proyectadas en los resúmenes.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Se cita el cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normatividad estatal vigente. Otros requisitos específicos: No especificado.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IMPI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14/07/2026 1400</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,7 +1433,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1444,12 +1443,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1460,16 +1453,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1502,7 +1485,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1513,12 +1495,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1529,16 +1505,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1571,7 +1537,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1582,24 +1547,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1632,7 +1579,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1643,24 +1589,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1693,7 +1621,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1704,12 +1631,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1720,16 +1641,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1762,7 +1673,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1773,12 +1683,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1789,16 +1693,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1831,7 +1725,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -1842,24 +1735,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1892,7 +1767,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -1903,12 +1777,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1962,9 +1830,6 @@
           <t>Se cita el cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normatividad estatal vigente. Otros requisitos específicos: No especificado.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1977,19 +1842,16 @@
           <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Hidalgo</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2000,24 +1862,6 @@
           <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2030,19 +1874,16 @@
           <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>14/07/2026 1400</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2053,24 +1894,774 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Las licitaciones tienen fechas de apertura entre el 03 y 08 de julio de 2026, y fallos programados entre el 03 y 09 de julio de 2026. La vigencia no está especificada por contrato individual en los resúmenes.</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Material de oficina, servicios de impresión de libros, servicios de congresos y convenciones, arrendamiento de maquinaria, servicios de evaluación de resultados (FAISM), vehículos y lámparas de alumbrado público. Modalidades de pago y suministros de consumibles no especificados.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Varias instituciones: Policía Industrial Bancaria (Pachuca), Instituto Hidalguense de Educación (Pachuca), Municipio de Huejutla de Reyes (Palacio Municipal), Municipio de Mineral de la Reforma (Pachuquilla) y Municipio de Actopan (Calle Hidalgo No. 8).</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria | 1 concepto | Material de oficina; Instituto Hidalguense | 2 y 3 partidas | Impresión de libros y congresos; Huejutla | 3 partidas únicas | Maquinaria, evaluación de resultados y vehículos; Mineral de la Reforma | 2 partidas | Lámparas suburbanas; Actopan | 1 partida | Motoniveladora nueva.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Volúmenes totales no especificados, solo se mencionan partidas por concepto.</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Se cita el cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normatividad estatal. No se detallan NOMs o licencias específicas adicionales.</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IMPI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>14/07/2026 1400</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INICACH</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>065P04 - SECRETARA DE PLANEACIN, FINANZAS Y ADMINISTR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>23/07/2026 1200</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1926,7 +1926,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -1937,12 +1936,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1953,16 +1946,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1995,7 +1978,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2006,12 +1988,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2022,16 +1998,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2064,7 +2030,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2075,24 +2040,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2125,7 +2072,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2136,24 +2082,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2186,7 +2114,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2197,12 +2124,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2213,16 +2134,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2255,7 +2166,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2266,12 +2176,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2282,16 +2186,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2324,7 +2218,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2335,24 +2228,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2385,7 +2260,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2396,12 +2270,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2447,9 +2315,6 @@
           <t>Se cita el cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y normatividad estatal. No se detallan NOMs o licencias específicas adicionales.</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2462,19 +2327,16 @@
           <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Hidalgo</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2485,24 +2347,6 @@
           <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2515,19 +2359,16 @@
           <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>14/07/2026 1400</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2538,24 +2379,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2568,19 +2391,16 @@
           <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2591,24 +2411,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2621,19 +2423,16 @@
           <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>23/07/2026 1200</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2644,24 +2443,781 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Diversas licitaciones con apertura de propuestas entre el 03 y 08 de julio de 2026 y fallos entre el 03 y 09 de julio de 2026. Vigencia de contrato: No especificado en los resúmenes de convocatoria.</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Adquisiciones diversas: material de oficina, impresión de libros, servicios de congresos, arrendamiento de maquinaria, evaluación de resultados (FAISM), vehículos, lámparas de alumbrado público y una motoniveladora. Consumibles y modalidad de pago: No especificado.</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria (Pachuca); Instituto Hidalguense de Educación (Pachuca); Municipios de Huejutla de Reyes, Mineral de la Reforma y Actopan, Hidalgo.</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>• PIBEH (PIBEH-LP-08-2026): Material de oficina | 1 concepto
+• IHE (IHE-CGAyF-N36-2026): Impresión de libros | 2 partidas
+• IHE (IHE-CGAyF-N37-2026): Servicio de congresos | 3 partidas
+• Huejutla (PMH-028-FEXHI-LP-2026-018): Arrendamiento de maquinaria | Partida única
+• Huejutla (PMH-028-FAPFM-LP-2026-014): Evaluación FAISM | Partida única
+• Huejutla (PMH-028-FDOGP-LP-2026-017): Vehículo general | Partida única
+• Mineral de la Reforma (FORTAMUN-LP42-2026): Lámparas suburbanas | 2 partidas
+• Actopan (LP-PMAH-ADQ-002-2026): Motoniveladora nueva | 1 partida</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>No especificado volumen operativo detallado (ej. número de unidades exactas o servicios proyectados más allá de las partidas mencionadas).</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Se exige cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y su Reglamento. Partnerships o NOMs específicas: No especificado.</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IMPI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>14/07/2026 1400</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>INICACH</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>065P04 - SECRETARA DE PLANEACIN, FINANZAS Y ADMINISTR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>23/07/2026 1200</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,7 +2475,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2486,12 +2485,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2502,16 +2495,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2544,7 +2527,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2555,12 +2537,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2571,16 +2547,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2613,7 +2579,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2624,24 +2589,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2674,7 +2621,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2685,24 +2631,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2735,7 +2663,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2746,12 +2673,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2762,16 +2683,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2804,7 +2715,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -2815,12 +2725,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2831,16 +2735,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2873,7 +2767,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2884,24 +2777,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2934,7 +2809,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -2945,12 +2819,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3003,9 +2871,6 @@
           <t>Se exige cumplimiento de la Ley de Adquisiciones, Arrendamientos y Servicios del Sector Público del Estado de Hidalgo y su Reglamento. Partnerships o NOMs específicas: No especificado.</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3018,19 +2883,16 @@
           <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Hidalgo</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3041,24 +2903,6 @@
           <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3071,19 +2915,16 @@
           <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>14/07/2026 1400</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3094,24 +2935,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3124,19 +2947,16 @@
           <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3147,24 +2967,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3177,19 +2979,16 @@
           <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>23/07/2026 1200</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3200,24 +2999,782 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CECYTECH</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE 22 LOTES DE MATERIALES DE IMPRESION Y RE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IA-66-015-907025980-N-2-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CONTRATACIÓN DE SERVICIO DE IMPRESIÓN DE MATERIAL DE DI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IA-20-139-020000998-N-22-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>08/07/2026 1500</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEFINCOAHUILA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE SOFTWARE, EQUIPAMIENTO E INSUMOS DE LABO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LA-64-O78-905002984-I-1-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>20/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CINVESTAV</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE EQUIPO DE LABORATORIO PARA EL CINVESTAV</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LA-11-L4J-011L4J999-N-814-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>15/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IA-20-125-020000021-N-23-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>07/07/2026 1300</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BIENESTAR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIÓN Y ELABORACIÓN DE MATERIAL INFORMA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IA-20-150-020000004-N-33-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Poder Judicial del Estado de Sonora</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Prestación de Servicios de Fotocopiado, Impresión y Esc</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PJESON-LP-26-0601</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Instituto Hidalguense de Educación</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Servicio de impresión de libros</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IHE-CGAyF-N36-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>El documento contiene diversas licitaciones con aperturas entre el 3 y 8 de julio de 2026 y fallos entre el 3 y 9 de julio de 2026. La vigencia del contrato no está especificada en ninguno de los resúmenes de convocatoria.</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Diversos bienes y servicios: material de oficina (PIBEH), impresión de libros (IHE), congresos y convenciones (IHE), arrendamiento de maquinaria (Huejutla), evaluación FAISM (Huejutla), vehículos (Huejutla), lámparas de alumbrado público (Mineral de la Reforma) y una motoniveladora (Actopan). No se especifica quién suministra consumibles ni la modalidad de pago.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Policía Industrial Bancaria (Calle Fundadores 210-a, Pachuca), IHE (Blvd. Felipe Ángeles s/n, Pachuca), Municipio de Huejutla (Palacio Municipal s/n, Col. Centro, Huejutla), Mineral de la Reforma (Av. Francisco I. Madero S/N, Pachuquilla), Municipio de Actopan (Calle Hidalgo 8, Col. Centro, Actopan).</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Tabla en texto: 
+- PIBEH | 1 concepto | Material de oficina
+- IHE | 2 partidas | Servicio de impresión de libros
+- IHE | 3 partidas | Servicio de congresos y convenciones
+- Huejutla | Partida única | Arrendamiento de maquinaria
+- Huejutla | Partida única | Evaluación FAISM
+- Huejutla | Partida única | Vehículo en general
+- Mineral de la Reforma | 2 partidas | Lámparas suburbanas
+- Actopan | 1 partida | Motoniveladora nueva</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>El volumen operativo no ha sido detallado, solo se mencionan cantidades de partidas por licitación.</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>No especificado.</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IMPI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>14/07/2026 1400</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>INICACH</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>065P04 - SECRETARA DE PLANEACIN, FINANZAS Y ADMINISTR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>23/07/2026 1200</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA63"/>
+  <dimension ref="A1:AA70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,7 +3031,6 @@
           <t>06/07/2026 1000</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3042,12 +3041,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/12241eb3ffdc41ada5e10d89ac1214d0/procedimiento</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3058,16 +3051,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3100,7 +3083,6 @@
           <t>08/07/2026 1500</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3111,12 +3093,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/75d2bcfd22df493383cb62eb057645f7/procedimiento</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3127,16 +3103,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3169,7 +3135,6 @@
           <t>20/07/2026 1000</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3180,24 +3145,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/2c6e04e3e26447b39a0c7300090d5c46/procedimiento</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3230,7 +3177,6 @@
           <t>15/07/2026 1100</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3241,24 +3187,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/384ca4b00fd14a059ec078c1d728faaa/procedimiento</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3291,7 +3219,6 @@
           <t>07/07/2026 1300</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3302,12 +3229,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/70831d7034614ef68fd178e16ccb56f5/procedimiento</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3318,16 +3239,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3360,7 +3271,6 @@
           <t>10/07/2026 1000</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3371,12 +3281,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/e4ad67f9ed7a42c497360b375b516164/procedimiento</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3387,16 +3291,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3429,7 +3323,6 @@
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3440,24 +3333,6 @@
           <t>https://licitary.mx/docs5/SON300626fevwyubifjerkgeg.png</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3490,7 +3365,6 @@
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3501,12 +3375,6 @@
           <t>https://licitary.mx/docs5/HGO300626fevdvfth4653t4ewfegw.pdf</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3560,9 +3428,6 @@
           <t>No especificado.</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3575,19 +3440,16 @@
           <t>Materiales, tiles y Equipos Menores de Tecnologas de</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Hidalgo</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3598,24 +3460,6 @@
           <t>https://eoficialia.hidalgo.gob.mx/LICITACIONES/Recursos/Temporal/888_0_0.pdf</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3628,19 +3472,16 @@
           <t>SERVICIO PLURIANUAL DE DIGITALIZACIN Y CAPTURA DE DOCU</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>14/07/2026 1400</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3651,24 +3492,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4366da6b8368408fb7b9fbd4aa60ae9a/procedimiento</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3681,19 +3504,16 @@
           <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3704,24 +3524,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3734,19 +3536,16 @@
           <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>23/07/2026 1200</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3757,24 +3556,385 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEPOMEX</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ARRENDAMIENTO DE EQUIPO DE IMPRESIN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>22/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/1f8add4857c44784bcb246114339ee2f/procedimiento</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEDENA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIN DE LA 5/A. SECCIN DEL HOSP. CNTL. MIL.: E</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>12/08/2026 0900</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/617e250b22e14ba48d566cdd303d8e05/procedimiento</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IMSS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SERVICIO MDICO INTEGRAL PARA LA DIGITALIZACIN POST PR</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>13/07/2026 0900</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/94943f41100048ff847441367d1a8a4b/procedimiento</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LECHEPARAELBIENESTAR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIN DE FORMATOS DE LA TARJETA DE DOTA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>09/07/2026 1100</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/fc7b6ac6880e49889d38abf57dbe31ec/procedimiento</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>INICACH</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>065P04 - SECRETARA DE PLANEACIN, FINANZAS Y ADMINISTR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>23/07/2026 1200</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SNICS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIN DE ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/c5c0629f3a4a466e89bb06dc08da0d48/procedimiento</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA70"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3568,19 +3568,16 @@
           <t>ARRENDAMIENTO DE EQUIPO DE IMPRESIN OPERATIVA</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>22/07/2026 1100</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3591,12 +3588,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/1f8add4857c44784bcb246114339ee2f/procedimiento</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3607,16 +3598,6 @@
           <t>Requiere revisión manual (liga dinámica o sin PDF directo).</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3629,19 +3610,16 @@
           <t>CONSTRUCCIN DE LA 5/A. SECCIN DEL HOSP. CNTL. MIL.: E</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>12/08/2026 0900</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3652,24 +3630,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/617e250b22e14ba48d566cdd303d8e05/procedimiento</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3682,19 +3642,16 @@
           <t>SERVICIO MDICO INTEGRAL PARA LA DIGITALIZACIN POST PR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>13/07/2026 0900</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3705,24 +3662,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/94943f41100048ff847441367d1a8a4b/procedimiento</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3735,19 +3674,16 @@
           <t>SERVICIO DE IMPRESIN DE FORMATOS DE LA TARJETA DE DOTA</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>09/07/2026 1100</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3758,24 +3694,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/fc7b6ac6880e49889d38abf57dbe31ec/procedimiento</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3788,19 +3706,16 @@
           <t>ADQUISICION DE LAS PARTIDAS 21101. MATERIALES Y UTILES</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3811,24 +3726,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/9ae9c522ac334d668d4636fae2f68a77/procedimiento</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3841,19 +3738,16 @@
           <t>SERVICIO DE DESARROLLO DE SOFTWARE Y ADQUISICIN DE EQU</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>23/07/2026 1200</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3864,24 +3758,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/4543ade7533d4d9d92ba28230e41df9b/procedimiento</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3894,19 +3770,16 @@
           <t>SERVICIO DE IMPRESIN DE ETIQUETAS</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -3917,24 +3790,271 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/c5c0629f3a4a466e89bb06dc08da0d48/procedimiento</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Consejo Mexiquense de Ciencia y Tecnologa (COMECYT)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>servicio de Impresin de Documentos Oficiales de la rev</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/Bases IRP-005-2026rgth5yj76h54tgrew.pdf</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Consejo Mexiquense de Ciencia y Tecnologa (COMECYT)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>contratacin del servicio para impresin de documentos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://licitary.mx/docs5/Bases IRP-006-2026fwregth4yj576k87jhtr.pdf</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>COMISIN DE AGUA POTABLE ALCANTARILLADO Y SANEAMIENTO D</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gastos Indirectos (Servicios de apoyo administrativo, f</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://compranet.guerrero.gob.mx/PublicTempStorage%5CICMTP-013-022-2026%5CBases.pdf</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Municipio de Guadalajara, Jalisco</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CONTRATACIN DE SERVICIO DE IMPRESIN DE PALIACATES Y C</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Licitary</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://transparencia.guadalajara.gob.mx/sites/default/files/uploads/768427e900/CONVOCATORIA%20LSCC-GDL-072-2026..pdf</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SNICS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPRESIN DE ETIQUETAS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>14/07/2026 1000</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Compras MX</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/c5c0629f3a4a466e89bb06dc08da0d48/procedimiento</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Licitaciones.xlsx
+++ b/Licitaciones.xlsx
@@ -3802,19 +3802,16 @@
           <t>servicio de Impresin de Documentos Oficiales de la rev</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3825,24 +3822,6 @@
           <t>https://licitary.mx/docs5/Bases IRP-005-2026rgth5yj76h54tgrew.pdf</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3855,19 +3834,16 @@
           <t>contratacin del servicio para impresin de documentos</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3878,24 +3854,6 @@
           <t>https://licitary.mx/docs5/Bases IRP-006-2026fwregth4yj576k87jhtr.pdf</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3908,19 +3866,16 @@
           <t>Gastos Indirectos (Servicios de apoyo administrativo, f</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3931,24 +3886,6 @@
           <t>https://compranet.guerrero.gob.mx/PublicTempStorage%5CICMTP-013-022-2026%5CBases.pdf</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3961,19 +3898,16 @@
           <t>CONTRATACIN DE SERVICIO DE IMPRESIN DE PALIACATES Y C</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Jalisco</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Licitary</t>
@@ -3984,24 +3918,6 @@
           <t>https://transparencia.guadalajara.gob.mx/sites/default/files/uploads/768427e900/CONVOCATORIA%20LSCC-GDL-072-2026..pdf</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4014,19 +3930,16 @@
           <t>SERVICIO DE IMPRESIN DE ETIQUETAS</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>14/07/2026 1000</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Compras MX</t>
@@ -4037,24 +3950,6 @@
           <t>https://comprasmx.buengobierno.gob.mx/sitiopublico/#/sitiopublico/detalle/c5c0629f3a4a466e89bb06dc08da0d48/procedimiento</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
